--- a/artfynd/A 33184-2025 artfynd.xlsx
+++ b/artfynd/A 33184-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126882325</v>
+        <v>126882310</v>
       </c>
       <c r="B2" t="n">
-        <v>57654</v>
+        <v>57817</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -784,10 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126882310</v>
+        <v>126882325</v>
       </c>
       <c r="B3" t="n">
-        <v>57817</v>
+        <v>57654</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -795,21 +795,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">

--- a/artfynd/A 33184-2025 artfynd.xlsx
+++ b/artfynd/A 33184-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126882310</v>
+        <v>126882325</v>
       </c>
       <c r="B2" t="n">
-        <v>57817</v>
+        <v>57654</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -784,10 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126882325</v>
+        <v>126882310</v>
       </c>
       <c r="B3" t="n">
-        <v>57654</v>
+        <v>57817</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -795,21 +795,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">

--- a/artfynd/A 33184-2025 artfynd.xlsx
+++ b/artfynd/A 33184-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126882325</v>
+        <v>126882310</v>
       </c>
       <c r="B2" t="n">
-        <v>57654</v>
+        <v>57821</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -784,10 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126882310</v>
+        <v>126882325</v>
       </c>
       <c r="B3" t="n">
-        <v>57817</v>
+        <v>57658</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -795,21 +795,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">

--- a/artfynd/A 33184-2025 artfynd.xlsx
+++ b/artfynd/A 33184-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126882310</v>
+        <v>126882325</v>
       </c>
       <c r="B2" t="n">
-        <v>57821</v>
+        <v>57658</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -784,10 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126882325</v>
+        <v>126882310</v>
       </c>
       <c r="B3" t="n">
-        <v>57658</v>
+        <v>57821</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -795,21 +795,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">

--- a/artfynd/A 33184-2025 artfynd.xlsx
+++ b/artfynd/A 33184-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126882325</v>
       </c>
       <c r="B2" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>126882310</v>
       </c>
       <c r="B3" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
